--- a/test/list/panjalu/sandingtaman/db/list_sandingtaman_db.xlsx
+++ b/test/list/panjalu/sandingtaman/db/list_sandingtaman_db.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\wdio-dds\test\list\panjalu\sandingtaman\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F6D62F-C37B-4478-98BE-373A7873A212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC211411-63DD-40D3-94CA-1446E04E7B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4A4170CD-5F29-480B-944E-1B0FEA867C5C}"/>
   </bookViews>
@@ -19,10 +19,21 @@
   <externalReferences>
     <externalReference r:id="rId3"/>
   </externalReferences>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -504,7 +515,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -553,7 +564,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -565,7 +576,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Mata Uang" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -603,7 +614,7 @@
       <sheetName val="conf"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="2">
           <cell r="A2" t="str">
@@ -756,7 +767,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1104,11 +1115,11 @@
       </c>
       <c r="E2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>006</v>
       </c>
       <c r="F2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>008</v>
       </c>
       <c r="G2" s="3" t="str">
         <f>conf!$A$2</f>
@@ -1134,7 +1145,7 @@
       </c>
       <c r="D3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Nanggela</v>
+        <v>Karoya</v>
       </c>
       <c r="E3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -1142,7 +1153,7 @@
       </c>
       <c r="F3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>009</v>
       </c>
       <c r="G3" s="3" t="str">
         <f>conf!$A$2</f>
@@ -1168,15 +1179,15 @@
       </c>
       <c r="D4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cipicung</v>
+        <v>Sindangjaya</v>
       </c>
       <c r="E4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>002</v>
       </c>
       <c r="F4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>001</v>
       </c>
       <c r="G4" s="3" t="str">
         <f>conf!$A$2</f>
@@ -1206,7 +1217,7 @@
       </c>
       <c r="E5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>010</v>
       </c>
       <c r="F5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -1236,15 +1247,15 @@
       </c>
       <c r="D6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Karoya</v>
+        <v>Cipicung</v>
       </c>
       <c r="E6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>001</v>
       </c>
       <c r="F6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
+        <v>003</v>
       </c>
       <c r="G6" s="3" t="str">
         <f>conf!$A$2</f>
@@ -1270,15 +1281,15 @@
       </c>
       <c r="D7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cipicung</v>
+        <v>Sindangjaya</v>
       </c>
       <c r="E7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>001</v>
       </c>
       <c r="F7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>012</v>
       </c>
       <c r="G7" s="3" t="str">
         <f>conf!$A$2</f>
@@ -1304,15 +1315,15 @@
       </c>
       <c r="D8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sanding</v>
+        <v>Karoya</v>
       </c>
       <c r="E8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>005</v>
       </c>
       <c r="F8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>006</v>
       </c>
       <c r="G8" s="3" t="str">
         <f>conf!$A$2</f>
@@ -1338,15 +1349,15 @@
       </c>
       <c r="D9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Nanggela</v>
+        <v>Karoya</v>
       </c>
       <c r="E9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>009</v>
       </c>
       <c r="F9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>011</v>
       </c>
       <c r="G9" s="3" t="str">
         <f>conf!$A$2</f>
@@ -1372,15 +1383,15 @@
       </c>
       <c r="D10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Karoya</v>
+        <v>Cidarma</v>
       </c>
       <c r="E10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>004</v>
       </c>
       <c r="F10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>004</v>
       </c>
       <c r="G10" s="3" t="str">
         <f>conf!$A$2</f>
@@ -1406,15 +1417,15 @@
       </c>
       <c r="D11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sanding</v>
+        <v>Nanggela</v>
       </c>
       <c r="E11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>002</v>
       </c>
       <c r="F11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>013</v>
       </c>
       <c r="G11" s="3" t="str">
         <f>conf!$A$2</f>
@@ -1440,11 +1451,11 @@
       </c>
       <c r="D12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Nanggela</v>
+        <v>Citaman</v>
       </c>
       <c r="E12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>003</v>
       </c>
       <c r="F12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -1474,15 +1485,15 @@
       </c>
       <c r="D13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Karoya</v>
+        <v>Sindangjaya</v>
       </c>
       <c r="E13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>004</v>
       </c>
       <c r="F13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>014</v>
       </c>
       <c r="G13" s="3" t="str">
         <f>conf!$A$2</f>
@@ -1508,15 +1519,15 @@
       </c>
       <c r="D14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sindangjaya</v>
+        <v>Cidarma</v>
       </c>
       <c r="E14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>015</v>
       </c>
       <c r="F14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>004</v>
       </c>
       <c r="G14" s="3" t="str">
         <f>conf!$A$2</f>
@@ -1546,7 +1557,7 @@
       </c>
       <c r="E15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>002</v>
       </c>
       <c r="F15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -1576,15 +1587,15 @@
       </c>
       <c r="D16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cidarma</v>
+        <v>Cipicung</v>
       </c>
       <c r="E16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>011</v>
       </c>
       <c r="F16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>013</v>
       </c>
       <c r="G16" s="3" t="str">
         <f>conf!$A$2</f>
@@ -1610,15 +1621,15 @@
       </c>
       <c r="D17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cidarma</v>
+        <v>Nanggela</v>
       </c>
       <c r="E17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>005</v>
       </c>
       <c r="F17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>012</v>
       </c>
       <c r="G17" s="3" t="str">
         <f>conf!$A$2</f>
@@ -1644,15 +1655,15 @@
       </c>
       <c r="D18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Citaman</v>
+        <v>Sindangjaya</v>
       </c>
       <c r="E18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>001</v>
       </c>
       <c r="F18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>003</v>
       </c>
       <c r="G18" s="3" t="str">
         <f>conf!$A$2</f>
@@ -1678,11 +1689,11 @@
       </c>
       <c r="D19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cidarma</v>
+        <v>Citaman</v>
       </c>
       <c r="E19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>015</v>
       </c>
       <c r="F19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -1712,15 +1723,15 @@
       </c>
       <c r="D20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Karoya</v>
+        <v>Sindangjaya</v>
       </c>
       <c r="E20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>013</v>
       </c>
       <c r="F20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>010</v>
       </c>
       <c r="G20" s="3" t="str">
         <f>conf!$A$2</f>
@@ -1746,15 +1757,15 @@
       </c>
       <c r="D21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Karoya</v>
+        <v>Cipicung</v>
       </c>
       <c r="E21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>013</v>
       </c>
       <c r="F21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>005</v>
       </c>
       <c r="G21" s="3" t="str">
         <f>conf!$A$2</f>
@@ -1780,15 +1791,15 @@
       </c>
       <c r="D22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Karoya</v>
+        <v>Cipicung</v>
       </c>
       <c r="E22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>015</v>
       </c>
       <c r="F22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>001</v>
       </c>
       <c r="G22" s="3" t="str">
         <f>conf!$A$2</f>
@@ -1814,15 +1825,15 @@
       </c>
       <c r="D23" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cipicung</v>
+        <v>Cidarma</v>
       </c>
       <c r="E23" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>013</v>
       </c>
       <c r="F23" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>004</v>
       </c>
       <c r="G23" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -1848,11 +1859,11 @@
       </c>
       <c r="E24" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>006</v>
+        <v>015</v>
       </c>
       <c r="F24" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>004</v>
       </c>
       <c r="G24" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -1878,11 +1889,11 @@
       </c>
       <c r="E25" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>001</v>
       </c>
       <c r="F25" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>014</v>
       </c>
       <c r="G25" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -1904,15 +1915,15 @@
       </c>
       <c r="D26" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cipicung</v>
+        <v>Sanding</v>
       </c>
       <c r="E26" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>004</v>
       </c>
       <c r="F26" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>005</v>
       </c>
       <c r="G26" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -1934,15 +1945,15 @@
       </c>
       <c r="D27" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sindangjaya</v>
+        <v>Karoya</v>
       </c>
       <c r="E27" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>008</v>
       </c>
       <c r="F27" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>004</v>
       </c>
       <c r="G27" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -1964,15 +1975,15 @@
       </c>
       <c r="D28" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cipicung</v>
+        <v>Sanding</v>
       </c>
       <c r="E28" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>007</v>
       </c>
       <c r="F28" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>011</v>
       </c>
       <c r="G28" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -1998,11 +2009,11 @@
       </c>
       <c r="E29" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>015</v>
       </c>
       <c r="F29" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>010</v>
       </c>
       <c r="G29" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2024,11 +2035,11 @@
       </c>
       <c r="D30" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sanding</v>
+        <v>Citaman</v>
       </c>
       <c r="E30" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>005</v>
       </c>
       <c r="F30" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -2054,15 +2065,15 @@
       </c>
       <c r="D31" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cipicung</v>
+        <v>Nanggela</v>
       </c>
       <c r="E31" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>006</v>
       </c>
       <c r="F31" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>003</v>
       </c>
       <c r="G31" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2088,11 +2099,11 @@
       </c>
       <c r="E32" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>009</v>
       </c>
       <c r="F32" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>012</v>
       </c>
       <c r="G32" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2114,15 +2125,15 @@
       </c>
       <c r="D33" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cidarma</v>
+        <v>Sanding</v>
       </c>
       <c r="E33" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>007</v>
       </c>
       <c r="F33" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>014</v>
       </c>
       <c r="G33" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2144,11 +2155,11 @@
       </c>
       <c r="D34" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Nanggela</v>
+        <v>Karoya</v>
       </c>
       <c r="E34" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>011</v>
       </c>
       <c r="F34" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -2174,15 +2185,15 @@
       </c>
       <c r="D35" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sindangjaya</v>
+        <v>Karoya</v>
       </c>
       <c r="E35" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>002</v>
       </c>
       <c r="F35" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>007</v>
       </c>
       <c r="G35" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2212,7 +2223,7 @@
       </c>
       <c r="F36" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>006</v>
       </c>
       <c r="G36" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2234,15 +2245,15 @@
       </c>
       <c r="D37" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sindangjaya</v>
+        <v>Citaman</v>
       </c>
       <c r="E37" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>013</v>
       </c>
       <c r="F37" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>004</v>
       </c>
       <c r="G37" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2264,15 +2275,15 @@
       </c>
       <c r="D38" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Karoya</v>
+        <v>Nanggela</v>
       </c>
       <c r="E38" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>009</v>
+      </c>
+      <c r="F38" s="2" t="str">
+        <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>013</v>
-      </c>
-      <c r="F38" s="2" t="str">
-        <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
       </c>
       <c r="G38" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2294,15 +2305,15 @@
       </c>
       <c r="D39" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sindangjaya</v>
+        <v>Cidarma</v>
       </c>
       <c r="E39" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>011</v>
       </c>
       <c r="F39" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>009</v>
       </c>
       <c r="G39" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2324,15 +2335,15 @@
       </c>
       <c r="D40" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Citaman</v>
+        <v>Karoya</v>
       </c>
       <c r="E40" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>014</v>
       </c>
       <c r="F40" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>007</v>
       </c>
       <c r="G40" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2354,15 +2365,15 @@
       </c>
       <c r="D41" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Karoya</v>
+        <v>Cipicung</v>
       </c>
       <c r="E41" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>011</v>
       </c>
       <c r="F41" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>006</v>
       </c>
       <c r="G41" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2384,15 +2395,15 @@
       </c>
       <c r="D42" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Citaman</v>
+        <v>Karoya</v>
       </c>
       <c r="E42" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>008</v>
       </c>
       <c r="F42" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>013</v>
       </c>
       <c r="G42" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2414,15 +2425,15 @@
       </c>
       <c r="D43" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sanding</v>
+        <v>Nanggela</v>
       </c>
       <c r="E43" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>006</v>
+        <v>010</v>
       </c>
       <c r="F43" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>005</v>
       </c>
       <c r="G43" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2444,7 +2455,7 @@
       </c>
       <c r="D44" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Citaman</v>
+        <v>Sanding</v>
       </c>
       <c r="E44" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -2474,15 +2485,15 @@
       </c>
       <c r="D45" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sanding</v>
+        <v>Citaman</v>
       </c>
       <c r="E45" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>012</v>
+        <v>015</v>
       </c>
       <c r="F45" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>006</v>
       </c>
       <c r="G45" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2504,15 +2515,15 @@
       </c>
       <c r="D46" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sanding</v>
+        <v>Citaman</v>
       </c>
       <c r="E46" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F46" s="2" t="str">
+        <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>004</v>
-      </c>
-      <c r="F46" s="2" t="str">
-        <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
       </c>
       <c r="G46" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2534,15 +2545,15 @@
       </c>
       <c r="D47" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Citaman</v>
+        <v>Sanding</v>
       </c>
       <c r="E47" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>015</v>
       </c>
       <c r="F47" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>004</v>
       </c>
       <c r="G47" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2564,11 +2575,11 @@
       </c>
       <c r="D48" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sindangjaya</v>
+        <v>Cipicung</v>
       </c>
       <c r="E48" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>009</v>
       </c>
       <c r="F48" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -2594,15 +2605,15 @@
       </c>
       <c r="D49" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Nanggela</v>
+        <v>Cidarma</v>
       </c>
       <c r="E49" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F49" s="2" t="str">
+        <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>008</v>
-      </c>
-      <c r="F49" s="2" t="str">
-        <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
       </c>
       <c r="G49" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2624,7 +2635,7 @@
       </c>
       <c r="D50" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sindangjaya</v>
+        <v>Citaman</v>
       </c>
       <c r="E50" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -2632,7 +2643,7 @@
       </c>
       <c r="F50" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>006</v>
       </c>
       <c r="G50" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2654,15 +2665,15 @@
       </c>
       <c r="D51" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Citaman</v>
+        <v>Karoya</v>
       </c>
       <c r="E51" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>005</v>
       </c>
       <c r="F51" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>004</v>
       </c>
       <c r="G51" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2684,15 +2695,15 @@
       </c>
       <c r="D52" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sanding</v>
+        <v>Citaman</v>
       </c>
       <c r="E52" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>010</v>
       </c>
       <c r="F52" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>006</v>
       </c>
       <c r="G52" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2714,15 +2725,15 @@
       </c>
       <c r="D53" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sindangjaya</v>
+        <v>Sanding</v>
       </c>
       <c r="E53" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>013</v>
       </c>
       <c r="F53" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>004</v>
       </c>
       <c r="G53" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2744,15 +2755,15 @@
       </c>
       <c r="D54" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Nanggela</v>
+        <v>Karoya</v>
       </c>
       <c r="E54" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>009</v>
       </c>
       <c r="F54" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>008</v>
       </c>
       <c r="G54" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2774,15 +2785,15 @@
       </c>
       <c r="D55" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Citaman</v>
+        <v>Nanggela</v>
       </c>
       <c r="E55" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>012</v>
+        <v>005</v>
       </c>
       <c r="F55" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>006</v>
       </c>
       <c r="G55" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2804,15 +2815,15 @@
       </c>
       <c r="D56" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sanding</v>
+        <v>Cidarma</v>
       </c>
       <c r="E56" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>006</v>
+        <v>012</v>
       </c>
       <c r="F56" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>011</v>
       </c>
       <c r="G56" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2834,15 +2845,15 @@
       </c>
       <c r="D57" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sanding</v>
+        <v>Nanggela</v>
       </c>
       <c r="E57" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>003</v>
       </c>
       <c r="F57" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>002</v>
       </c>
       <c r="G57" s="3" t="str">
         <f>[1]conf!$A$2</f>
@@ -2864,15 +2875,15 @@
       </c>
       <c r="D58" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Citaman</v>
+        <v>Sindangjaya</v>
       </c>
       <c r="E58" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>015</v>
       </c>
       <c r="F58" s="2" t="str">
         <f ca="1">INDEX([1]conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>013</v>
       </c>
       <c r="G58" s="3" t="str">
         <f>[1]conf!$A$2</f>
